--- a/donation_forms/023_military_support_donation_form--donation_forms.xlsx
+++ b/donation_forms/023_military_support_donation_form--donation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'cash',_'value':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Cash', 'value': 'cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'online_payment',_'value':_'online_payment'}</t>
+          <t>online_payment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Online Payment', 'value': 'online_payment'}</t>
+          <t>Online Payment</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card',_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Card', 'value': 'credit_card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'paypal',_'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal', 'value': 'paypal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'cash',_'value':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Cash', 'value': 'cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'online_payment',_'value':_'online_payment'}</t>
+          <t>online_payment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Online Payment', 'value': 'online_payment'}</t>
+          <t>Online Payment</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card',_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Card', 'value': 'credit_card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'paypal',_'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal', 'value': 'paypal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'accepted',_'value':_'accepted'}</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Accepted', 'value': 'accepted'}</t>
+          <t>Accepted</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'declined',_'value':_'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Declined', 'value': 'declined'}</t>
+          <t>Declined</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled', 'value': 'cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Completed', 'value': 'completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'not_refunded',_'value':_'not_refunded'}</t>
+          <t>not_refunded</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Not Refunded', 'value': 'not_refunded'}</t>
+          <t>Not Refunded</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'partially_refunded',_'value':_'partially_refunded'}</t>
+          <t>partially_refunded</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Partially Refunded', 'value': 'partially_refunded'}</t>
+          <t>Partially Refunded</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'fully_refunded',_'value':_'fully_refunded'}</t>
+          <t>fully_refunded</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Fully Refunded', 'value': 'fully_refunded'}</t>
+          <t>Fully Refunded</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'check',_'value':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Check', 'value': 'check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer',_'value':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Bank Transfer', 'value': 'bank_transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'paypal',_'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal', 'value': 'paypal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
